--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260812.xlsx
@@ -611,100 +611,100 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>138,385</t>
+          <t>137,885</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>29.44%</t>
+          <t>28.88%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>529,993,964</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>8.28%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>100,120</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.44%</t>
+          <t>8.21%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,865</t>
+          <t>99,870</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>7.70%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>343,004,636</t>
+          <t>50,715</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -721,56 +721,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>121,695</t>
+          <t>121,295</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,865,883</t>
+          <t>59,680</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>59,930</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -787,122 +787,122 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,835</t>
+          <t>65,615</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>18,273</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,373</t>
+          <t>45,265</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>45,265</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,825</t>
+          <t>77,045</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>77,305</t>
+          <t>20,295</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -919,56 +919,56 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,660</t>
+          <t>31,560</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>20,395</t>
+          <t>51,075</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>51,245</t>
+          <t>11,601</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -985,56 +985,56 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,658</t>
+          <t>26,558</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>19,530</t>
+          <t>36,280</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,400</t>
+          <t>19,430</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>59,648</t>
+          <t>59,448</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,636</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1117,56 +1117,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>21,408</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>11,701</t>
+          <t>127,055</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>127,475</t>
+          <t>19,617</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,617</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>37,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1249,34 +1249,34 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,490</t>
+          <t>43,350</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>37,690</t>
+          <t>1,482,418</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>290,526,720</t>
+          <t>32,874,620</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>316,535</t>
+          <t>604,987</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
